--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486666_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486666_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. KALINICENKO</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9933</v>
+        <v>1.7491</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6743</v>
+        <v>1.9775</v>
       </c>
       <c r="F2" t="n">
-        <v>0.319</v>
+        <v>-0.2284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0016</v>
+        <v>-0.2532</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1521</v>
+        <v>-0.4137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1537</v>
+        <v>0.1605</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9062</v>
+        <v>1.6577</v>
       </c>
       <c r="K2" t="n">
-        <v>1.09</v>
+        <v>0.9659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8161</v>
+        <v>0.6918</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9046</v>
+        <v>-1.9109</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2422</v>
+        <v>-1.3796</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6624</v>
+        <v>-0.5313</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1239</v>
+        <v>-0.1931</v>
       </c>
       <c r="R2" t="n">
-        <v>2.51</v>
+        <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.3378</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9926</v>
+        <v>0.2273</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2865</v>
+        <v>0.1105</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8995</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8995</v>
+        <v>0.2856</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.4135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>A. KALINICENKO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8525</v>
+        <v>1.5837</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0809</v>
+        <v>1.3641</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2284</v>
+        <v>0.2196</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2532</v>
+        <v>0.0016</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4137</v>
+        <v>-0.1521</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1605</v>
+        <v>0.1537</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6577</v>
+        <v>1.9062</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9659</v>
+        <v>1.09</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6918</v>
+        <v>0.8161</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9109</v>
+        <v>-1.9046</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3796</v>
+        <v>-1.2422</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5313</v>
+        <v>-0.6624</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1585</v>
+        <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4412</v>
+        <v>0.2965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3307</v>
+        <v>0.6823</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1105</v>
+        <v>-0.3858</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.8995</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2856</v>
+        <v>0.8995</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3377</v>
+        <v>1.5405</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4864</v>
+        <v>3.5899</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1487</v>
+        <v>-2.0494</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1076</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2924</v>
+        <v>-0.0897</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4135</v>
+        <v>0.5169</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7059</v>
+        <v>-0.6065</v>
       </c>
       <c r="V4" t="n">
         <v>0.6138</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2569</v>
+        <v>0.592</v>
       </c>
       <c r="E5" t="n">
-        <v>1.483</v>
+        <v>1.7932</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2261</v>
+        <v>-1.2013</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3005</v>
@@ -844,13 +844,13 @@
         <v>2.8962</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5351</v>
+        <v>-0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0272</v>
+        <v>0.3374</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5623</v>
+        <v>-0.5375</v>
       </c>
       <c r="V5" t="n">
         <v>2.1271</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4739</v>
+        <v>-0.4491</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0145</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4594</v>
+        <v>-0.4346</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4353</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0386</v>
+        <v>-0.0138</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7483</v>
+        <v>-2.195</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5016</v>
+        <v>1.881</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.2499</v>
+        <v>-4.076</v>
       </c>
       <c r="G7" t="n">
         <v>-3.6541</v>
@@ -1000,13 +1000,13 @@
         <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5463</v>
+        <v>-0.993</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5236</v>
+        <v>-0.097</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0699</v>
+        <v>-0.8961</v>
       </c>
       <c r="V7" t="n">
         <v>0.3282</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>F. QUERO CARMONA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.454</v>
+        <v>-3.1722</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2215</v>
+        <v>0.1254</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2325</v>
+        <v>-3.2977</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1501</v>
+        <v>-2.637</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4897</v>
+        <v>-3.1299</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6397</v>
+        <v>0.4929</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3163</v>
+        <v>1.5366</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2349</v>
+        <v>0.3881</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0814</v>
+        <v>1.1485</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1662</v>
+        <v>-4.1736</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7246</v>
+        <v>-3.518</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5583</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P8" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.1585</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9308</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9323</v>
+        <v>-0.1724</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.607</v>
+        <v>0.0755</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3253</v>
+        <v>-0.2479</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5133</v>
+        <v>-0.9421</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5133</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. QUERO CARMONA</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.59</v>
+        <v>-3.4043</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3917</v>
+        <v>-1.2215</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1984</v>
+        <v>-2.1828</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.637</v>
+        <v>0.1501</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.1299</v>
+        <v>-0.4897</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4929</v>
+        <v>0.6397</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5366</v>
+        <v>1.3163</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3881</v>
+        <v>1.2349</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1485</v>
+        <v>0.0814</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.1736</v>
+        <v>-1.1662</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.518</v>
+        <v>-1.7246</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.5583</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5792</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1585</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4416</v>
+        <v>-0.607</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1486</v>
+        <v>-0.2756</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9421</v>
+        <v>-1.5133</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6138</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6236</v>
+        <v>-5.7271</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8886</v>
+        <v>-2.9921</v>
       </c>
       <c r="F10" t="n">
         <v>-2.735</v>
@@ -1234,10 +1234,10 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6068</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0825</v>
+        <v>-0.0209</v>
       </c>
       <c r="U10" t="n">
         <v>-0.6892</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5068</v>
+        <v>-6.4738</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5143</v>
+        <v>-3.3074</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9925</v>
+        <v>-3.1663</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8795</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7447</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0603</v>
+        <v>-0.2342</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8842</v>
@@ -1348,7 +1348,7 @@
         <v>-15.9562</v>
       </c>
       <c r="E12" t="n">
-        <v>3.195600000000001</v>
+        <v>3.1956</v>
       </c>
       <c r="F12" t="n">
         <v>-19.1519</v>
@@ -1393,7 +1393,7 @@
         <v>-3.1721</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5489000000000002</v>
+        <v>0.5488000000000002</v>
       </c>
       <c r="U12" t="n">
         <v>-3.7209</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.1816</v>
+        <v>9.296099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.0146</v>
+        <v>8.7043</v>
       </c>
       <c r="F13" t="n">
-        <v>0.167</v>
+        <v>0.5918</v>
       </c>
       <c r="G13" t="n">
         <v>7.5654</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6508</v>
+        <v>0.7653</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.5169</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1763</v>
+        <v>0.2484</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.791</v>
+        <v>6.0629</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9012</v>
+        <v>7.0738</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1102</v>
+        <v>-1.0109</v>
       </c>
       <c r="G14" t="n">
         <v>5.819</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3348</v>
+        <v>0.6068</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4063</v>
+        <v>0.5789</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0279</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9421</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6796</v>
+        <v>4.83</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4796</v>
+        <v>1.6522</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.1778</v>
       </c>
       <c r="G15" t="n">
         <v>4.1929</v>
@@ -1624,13 +1624,13 @@
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2011</v>
+        <v>1.3515</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2959</v>
+        <v>0.4685</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9052</v>
+        <v>0.883</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.778</v>
+        <v>4.2317</v>
       </c>
       <c r="E16" t="n">
         <v>1.8753</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9026</v>
+        <v>2.3563</v>
       </c>
       <c r="G16" t="n">
         <v>1.23</v>
@@ -1702,13 +1702,13 @@
         <v>1.1585</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2084</v>
+        <v>0.6621</v>
       </c>
       <c r="T16" t="n">
         <v>0.1928</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0156</v>
+        <v>0.4693</v>
       </c>
       <c r="V16" t="n">
         <v>3.1118</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.737</v>
+        <v>3.5796</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8772</v>
+        <v>3.3943</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1402</v>
+        <v>0.1852</v>
       </c>
       <c r="G17" t="n">
         <v>2.3658</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6288</v>
+        <v>0.2137</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3863</v>
+        <v>0.1308</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2426</v>
+        <v>0.0829</v>
       </c>
       <c r="V17" t="n">
         <v>0.6138</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9012</v>
+        <v>2.4928</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4733</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4279</v>
+        <v>1.5024</v>
       </c>
       <c r="G18" t="n">
         <v>0.355</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.033</v>
+        <v>0.5586</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4966</v>
+        <v>0.0205</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4636</v>
+        <v>0.5381</v>
       </c>
       <c r="V18" t="n">
         <v>0.6138</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0574</v>
+        <v>1.2297</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5757</v>
+        <v>1.4723</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5183</v>
+        <v>-0.2425</v>
       </c>
       <c r="G19" t="n">
         <v>2.2655</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7998</v>
+        <v>0.9722</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9375</v>
+        <v>0.8341</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1377</v>
+        <v>0.1381</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6565</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8744</v>
+        <v>1.102</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7563</v>
+        <v>-0.6529</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6307</v>
+        <v>1.7549</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1878</v>
@@ -2014,13 +2014,13 @@
         <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2207</v>
+        <v>0.4483</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1377</v>
+        <v>0.2411</v>
       </c>
       <c r="U20" t="n">
-        <v>0.083</v>
+        <v>0.2072</v>
       </c>
       <c r="V20" t="n">
         <v>1.2277</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6017</v>
+        <v>-2.8871</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5821</v>
+        <v>0.2718</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1838</v>
+        <v>-3.159</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6939</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3199</v>
+        <v>0.0344</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2277</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4864</v>
+        <v>-3.0768</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.828</v>
+        <v>-1.5177</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6583</v>
+        <v>-1.559</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2837</v>
@@ -2170,13 +2170,13 @@
         <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6234</v>
+        <v>-0.2138</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>0.0344</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3475</v>
+        <v>-0.2481</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.399</v>
+        <v>-4.2503</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6218</v>
+        <v>-2.8978</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7773</v>
+        <v>-1.3525</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1253</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3349</v>
+        <v>-0.1862</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3311</v>
+        <v>0.3929</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0038</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6565</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5568</v>
+        <v>-5.2755</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.421</v>
+        <v>-1.2142</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1358</v>
+        <v>-4.0613</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8146</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9433</v>
+        <v>-0.6619</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1655</v>
+        <v>0.0413</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.7032</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7989</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.9563</v>
+        <v>17.3351</v>
       </c>
       <c r="E25" t="n">
-        <v>19.1519</v>
+        <v>19.15179999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1957</v>
+        <v>-1.816799999999999</v>
       </c>
       <c r="G25" t="n">
         <v>16.6883</v>
@@ -2404,13 +2404,13 @@
         <v>12.5501</v>
       </c>
       <c r="S25" t="n">
-        <v>3.172099999999999</v>
+        <v>4.550999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>3.721</v>
+        <v>3.721000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5487999999999998</v>
+        <v>0.8301000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.04279999999999951</v>
